--- a/artfynd/A 40718-2024 artfynd.xlsx
+++ b/artfynd/A 40718-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121072406</v>
+        <v>121072405</v>
       </c>
       <c r="B2" t="n">
-        <v>56552</v>
+        <v>78601</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,38 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>540482</v>
+        <v>540580</v>
       </c>
       <c r="R2" t="n">
-        <v>7202394</v>
+        <v>7202420</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -754,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121072405</v>
+        <v>121072406</v>
       </c>
       <c r="B3" t="n">
-        <v>78598</v>
+        <v>56555</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,34 +803,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540580</v>
+        <v>540482</v>
       </c>
       <c r="R3" t="n">
-        <v>7202420</v>
+        <v>7202394</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -866,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 40718-2024 artfynd.xlsx
+++ b/artfynd/A 40718-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121072405</v>
+        <v>121072406</v>
       </c>
       <c r="B2" t="n">
-        <v>78601</v>
+        <v>56555</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,38 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>540580</v>
+        <v>540482</v>
       </c>
       <c r="R2" t="n">
-        <v>7202420</v>
+        <v>7202394</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121072406</v>
+        <v>121072405</v>
       </c>
       <c r="B3" t="n">
-        <v>56555</v>
+        <v>78604</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,38 +807,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540482</v>
+        <v>540580</v>
       </c>
       <c r="R3" t="n">
-        <v>7202394</v>
+        <v>7202420</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -866,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD3" t="b">
